--- a/TimewaxSync/bin/Debug/Planning Timewax.xlsx
+++ b/TimewaxSync/bin/Debug/Planning Timewax.xlsx
@@ -476,7 +476,7 @@
 </file>
 
 <file path=vstoDataStore/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A3E408A-DBD4-4D27-BF35-8EAB9BB45B85}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAEB9018-FE7C-4F31-A07E-B7486536A993}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>